--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/magallanes.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/magallanes.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/magallanes.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/magallanes.xlsx
@@ -623,7 +623,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.730.436-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>77.754.348-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
